--- a/jogos_2025-06-06.xlsx
+++ b/jogos_2025-06-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -196,10 +142,10 @@
     <t>13:00</t>
   </si>
   <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:15</t>
   </si>
   <si>
     <t>19:00</t>
@@ -229,12 +175,12 @@
     <t>Norway Toppserien</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -262,15 +208,18 @@
     <t>Bodø / Glimt W</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
@@ -304,15 +253,18 @@
     <t>Trondheims-Ørn</t>
   </si>
   <si>
+    <t>New York City II</t>
+  </si>
+  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
@@ -331,10 +283,73 @@
     <t>Seattle Reign</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['45', '45+2', '86']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['-1', '-1']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['9', '26', '85']</t>
+  </si>
+  <si>
+    <t>['50', '70']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['9', '9006']</t>
+  </si>
+  <si>
+    <t>['15', '26']</t>
+  </si>
+  <si>
+    <t>['11', '41', '90+2']</t>
+  </si>
+  <si>
+    <t>['17', '28', '50', '69']</t>
+  </si>
+  <si>
+    <t>['-1', '-1', '-1']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
+  </si>
+  <si>
+    <t>['3', '31']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['48', '84', '90+2']</t>
+  </si>
+  <si>
+    <t>['67', '87']</t>
   </si>
 </sst>
 </file>
@@ -698,10 +713,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD15"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,103 +831,49 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45814</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L2">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="M2">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>1.67</v>
@@ -954,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -978,102 +939,48 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.67</v>
-      </c>
-      <c r="BC2">
-        <v>2.2</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>101</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45814.27083333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45814</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -1148,102 +1055,48 @@
         <v>1.07</v>
       </c>
       <c r="AJ3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="AK3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL3">
-        <v>2</v>
-      </c>
-      <c r="AM3">
-        <v>1.22</v>
-      </c>
-      <c r="AN3">
-        <v>1.17</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.34</v>
-      </c>
-      <c r="AQ3">
-        <v>1.65</v>
-      </c>
-      <c r="AR3">
-        <v>2.08</v>
-      </c>
-      <c r="AS3">
-        <v>2.78</v>
-      </c>
-      <c r="AT3">
-        <v>3.55</v>
-      </c>
-      <c r="AU3">
-        <v>2.78</v>
-      </c>
-      <c r="AV3">
-        <v>2.05</v>
-      </c>
-      <c r="AW3">
-        <v>1.6</v>
-      </c>
-      <c r="AX3">
-        <v>1.34</v>
-      </c>
-      <c r="AY3">
-        <v>1.23</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.7</v>
-      </c>
-      <c r="BC3">
-        <v>1.6</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>102</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45814.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45814</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" t="s">
-        <v>93</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L4">
         <v>3.24</v>
@@ -1318,433 +1171,271 @@
         <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AK4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL4">
-        <v>1.64</v>
-      </c>
-      <c r="AM4">
-        <v>1.28</v>
-      </c>
-      <c r="AN4">
-        <v>1.28</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.46</v>
-      </c>
-      <c r="AQ4">
-        <v>1.85</v>
-      </c>
-      <c r="AR4">
-        <v>2.42</v>
-      </c>
-      <c r="AS4">
-        <v>3.34</v>
-      </c>
-      <c r="AT4">
-        <v>4.25</v>
-      </c>
-      <c r="AU4">
-        <v>2.38</v>
-      </c>
-      <c r="AV4">
-        <v>1.81</v>
-      </c>
-      <c r="AW4">
-        <v>1.44</v>
-      </c>
-      <c r="AX4">
-        <v>1.24</v>
-      </c>
-      <c r="AY4">
-        <v>1.16</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.31</v>
-      </c>
-      <c r="BC4">
-        <v>1.76</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45814.29166666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45814</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L5">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="M5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
         <v>1.57</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q5">
         <v>3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC5">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.57</v>
-      </c>
-      <c r="BC5">
-        <v>3</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>104</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45814.45833333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45814</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK6" t="s">
         <v>105</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="3">
+      <c r="AL6" s="3">
         <v>45814.54166666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45814</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1753,332 +1444,224 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L7">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M7">
-        <v>3.06</v>
+        <v>3.85</v>
       </c>
       <c r="N7">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="P7">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="Q7">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="T7">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="U7">
+        <v>1.77</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
+      </c>
+      <c r="W7">
         <v>1.2</v>
       </c>
-      <c r="V7">
-        <v>10</v>
-      </c>
-      <c r="W7">
-        <v>1.02</v>
-      </c>
       <c r="X7">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>4.75</v>
+        <v>17</v>
       </c>
       <c r="Z7">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="AA7">
-        <v>2.14</v>
+        <v>5</v>
       </c>
       <c r="AB7">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="AC7">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>6.25</v>
+        <v>1.98</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="AF7">
-        <v>2.55</v>
+        <v>1.39</v>
       </c>
       <c r="AG7">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AH7">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="AI7">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="AK7" t="s">
         <v>106</v>
       </c>
-      <c r="AL7">
-        <v>1.4</v>
-      </c>
-      <c r="AM7">
-        <v>1.27</v>
-      </c>
-      <c r="AN7">
-        <v>1.95</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.54</v>
-      </c>
-      <c r="AQ7">
-        <v>2.16</v>
-      </c>
-      <c r="AR7">
-        <v>3.08</v>
-      </c>
-      <c r="AS7">
-        <v>3.44</v>
-      </c>
-      <c r="AT7">
-        <v>5.15</v>
-      </c>
-      <c r="AU7">
-        <v>2.5</v>
-      </c>
-      <c r="AV7">
-        <v>1.68</v>
-      </c>
-      <c r="AW7">
-        <v>1.47</v>
-      </c>
-      <c r="AX7">
-        <v>1.31</v>
-      </c>
-      <c r="AY7">
-        <v>1.16</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.53</v>
-      </c>
-      <c r="BC7">
-        <v>3.25</v>
-      </c>
-      <c r="BD7" s="3">
-        <v>45814.625</v>
+      <c r="AL7" s="3">
+        <v>45814.58333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45814</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="3">
-        <v>45814.70833333334</v>
+        <v>107</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>45814.63541666666</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45814</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2093,16 +1676,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L9">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M9">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="N9">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
         <v>1.73</v>
@@ -2120,138 +1703,84 @@
         <v>2.1</v>
       </c>
       <c r="T9">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="U9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V9">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.12</v>
+      </c>
+      <c r="Y9">
+        <v>5.3</v>
+      </c>
+      <c r="Z9">
+        <v>1.73</v>
+      </c>
+      <c r="AA9">
+        <v>2.07</v>
+      </c>
+      <c r="AB9">
+        <v>3.4</v>
+      </c>
+      <c r="AC9">
+        <v>1.35</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>1.06</v>
+      </c>
+      <c r="AF9">
+        <v>2.48</v>
+      </c>
+      <c r="AG9">
+        <v>1.42</v>
+      </c>
+      <c r="AH9">
+        <v>13</v>
+      </c>
+      <c r="AI9">
         <v>1.02</v>
       </c>
-      <c r="X9">
-        <v>1.08</v>
-      </c>
-      <c r="Y9">
-        <v>4.75</v>
-      </c>
-      <c r="Z9">
-        <v>1.57</v>
-      </c>
-      <c r="AA9">
-        <v>2.25</v>
-      </c>
-      <c r="AB9">
-        <v>2.9</v>
-      </c>
-      <c r="AC9">
-        <v>1.36</v>
-      </c>
-      <c r="AD9">
-        <v>6.5</v>
-      </c>
-      <c r="AE9">
-        <v>1.09</v>
-      </c>
-      <c r="AF9">
-        <v>2.45</v>
-      </c>
-      <c r="AG9">
-        <v>1.46</v>
-      </c>
-      <c r="AH9">
-        <v>12</v>
-      </c>
-      <c r="AI9">
-        <v>1.03</v>
-      </c>
       <c r="AJ9" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AK9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL9">
-        <v>1.38</v>
-      </c>
-      <c r="AM9">
-        <v>1.33</v>
-      </c>
-      <c r="AN9">
-        <v>1.62</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.53</v>
-      </c>
-      <c r="AQ9">
-        <v>2.01</v>
-      </c>
-      <c r="AR9">
-        <v>2.56</v>
-      </c>
-      <c r="AS9">
-        <v>3.4</v>
-      </c>
-      <c r="AT9">
-        <v>4.6</v>
-      </c>
-      <c r="AU9">
-        <v>2.3</v>
-      </c>
-      <c r="AV9">
-        <v>1.79</v>
-      </c>
-      <c r="AW9">
-        <v>1.47</v>
-      </c>
-      <c r="AX9">
-        <v>1.26</v>
-      </c>
-      <c r="AY9">
-        <v>1.15</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.73</v>
-      </c>
-      <c r="BC9">
-        <v>2.63</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>92</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45814.79166666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45814</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2263,165 +1792,111 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="N10">
+        <v>4.1</v>
+      </c>
+      <c r="O10">
+        <v>1.67</v>
+      </c>
+      <c r="P10">
         <v>7</v>
       </c>
-      <c r="O10">
-        <v>1.46</v>
-      </c>
-      <c r="P10">
-        <v>7.25</v>
-      </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="S10">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="U10">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
+        <v>1.17</v>
+      </c>
+      <c r="Y10">
+        <v>5.2</v>
+      </c>
+      <c r="Z10">
+        <v>1.66</v>
+      </c>
+      <c r="AA10">
+        <v>2</v>
+      </c>
+      <c r="AB10">
+        <v>3.28</v>
+      </c>
+      <c r="AC10">
+        <v>1.28</v>
+      </c>
+      <c r="AD10">
+        <v>7.4</v>
+      </c>
+      <c r="AE10">
         <v>1.08</v>
       </c>
-      <c r="Y10">
-        <v>7.5</v>
-      </c>
-      <c r="Z10">
+      <c r="AF10">
+        <v>2.5</v>
+      </c>
+      <c r="AG10">
         <v>1.42</v>
       </c>
-      <c r="AA10">
-        <v>2.9</v>
-      </c>
-      <c r="AB10">
-        <v>2.05</v>
-      </c>
-      <c r="AC10">
-        <v>1.61</v>
-      </c>
-      <c r="AD10">
-        <v>4.4</v>
-      </c>
-      <c r="AE10">
-        <v>1.2</v>
-      </c>
-      <c r="AF10">
-        <v>2.25</v>
-      </c>
-      <c r="AG10">
-        <v>1.6</v>
-      </c>
       <c r="AH10">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AK10" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL10">
-        <v>1.29</v>
-      </c>
-      <c r="AM10">
-        <v>1.26</v>
-      </c>
-      <c r="AN10">
-        <v>2.3</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.22</v>
-      </c>
-      <c r="AQ10">
-        <v>1.33</v>
-      </c>
-      <c r="AR10">
-        <v>1.6</v>
-      </c>
-      <c r="AS10">
-        <v>2</v>
-      </c>
-      <c r="AT10">
-        <v>2.6</v>
-      </c>
-      <c r="AU10">
-        <v>3.8</v>
-      </c>
-      <c r="AV10">
-        <v>2.65</v>
-      </c>
-      <c r="AW10">
-        <v>2.07</v>
-      </c>
-      <c r="AX10">
-        <v>1.71</v>
-      </c>
-      <c r="AY10">
-        <v>1.41</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.46</v>
-      </c>
-      <c r="BC10">
-        <v>3.4</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>92</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45814.79166666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45814</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2433,338 +1908,230 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L11">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="M11">
+        <v>3.3</v>
+      </c>
+      <c r="N11">
+        <v>5.25</v>
+      </c>
+      <c r="O11">
+        <v>1.46</v>
+      </c>
+      <c r="P11">
+        <v>7.25</v>
+      </c>
+      <c r="Q11">
         <v>3.4</v>
       </c>
-      <c r="N11">
-        <v>3.85</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA11">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AE11">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG11">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL11">
-        <v>1.35</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>1.5</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="3">
-        <v>45814.85416666666</v>
+        <v>92</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>45814.79166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45814</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L12">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N12">
-        <v>2.23</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
         <v>2.2</v>
       </c>
       <c r="P12">
-        <v>12.25</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
         <v>1.4</v>
       </c>
       <c r="V12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AD12">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AE12">
         <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AI12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL12">
-        <v>1.22</v>
-      </c>
-      <c r="AM12">
-        <v>1.26</v>
-      </c>
-      <c r="AN12">
-        <v>1.35</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.2</v>
-      </c>
-      <c r="BC12">
-        <v>1.73</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>108</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45814.85416666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45814</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2773,335 +2140,227 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L13">
+        <v>2.7</v>
+      </c>
+      <c r="M13">
+        <v>3.3</v>
+      </c>
+      <c r="N13">
+        <v>1.86</v>
+      </c>
+      <c r="O13">
+        <v>2.2</v>
+      </c>
+      <c r="P13">
+        <v>12.25</v>
+      </c>
+      <c r="Q13">
         <v>1.73</v>
       </c>
-      <c r="M13">
-        <v>3.75</v>
-      </c>
-      <c r="N13">
-        <v>3.75</v>
-      </c>
-      <c r="O13">
-        <v>1.5</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>2.6</v>
-      </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="T13">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="V13">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z13">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC13">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AD13">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AE13">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH13">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AI13">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AJ13" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AK13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL13">
-        <v>1.25</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1.95</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.5</v>
-      </c>
-      <c r="BC13">
-        <v>2.6</v>
-      </c>
-      <c r="BD13" s="3">
-        <v>45814.875</v>
+        <v>109</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>45814.85416666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45814</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
         <v>89</v>
       </c>
-      <c r="F14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>105</v>
-      </c>
       <c r="L14">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="M14">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="O14">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="S14">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="T14">
-        <v>3.22</v>
+        <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="V14">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z14">
+        <v>1.07</v>
+      </c>
+      <c r="AA14">
+        <v>5</v>
+      </c>
+      <c r="AB14">
+        <v>1.35</v>
+      </c>
+      <c r="AC14">
+        <v>2.62</v>
+      </c>
+      <c r="AD14">
+        <v>2</v>
+      </c>
+      <c r="AE14">
+        <v>1.73</v>
+      </c>
+      <c r="AF14">
         <v>1.36</v>
       </c>
-      <c r="AA14">
-        <v>2.75</v>
-      </c>
-      <c r="AB14">
-        <v>2.2</v>
-      </c>
-      <c r="AC14">
-        <v>1.55</v>
-      </c>
-      <c r="AD14">
-        <v>4.1</v>
-      </c>
-      <c r="AE14">
-        <v>1.18</v>
-      </c>
-      <c r="AF14">
-        <v>1.93</v>
-      </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>2.54</v>
       </c>
       <c r="AH14">
-        <v>8.199999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="AI14">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="AJ14" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL14">
-        <v>1.3</v>
-      </c>
-      <c r="AM14">
-        <v>1.25</v>
-      </c>
-      <c r="AN14">
-        <v>2.13</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.28</v>
-      </c>
-      <c r="AQ14">
-        <v>1.49</v>
-      </c>
-      <c r="AR14">
-        <v>1.77</v>
-      </c>
-      <c r="AS14">
-        <v>2.2</v>
-      </c>
-      <c r="AT14">
-        <v>2.8</v>
-      </c>
-      <c r="AU14">
-        <v>3.3</v>
-      </c>
-      <c r="AV14">
-        <v>2.43</v>
-      </c>
-      <c r="AW14">
-        <v>1.93</v>
-      </c>
-      <c r="AX14">
-        <v>1.58</v>
-      </c>
-      <c r="AY14">
-        <v>1.37</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.62</v>
-      </c>
-      <c r="BC14">
-        <v>2.85</v>
-      </c>
-      <c r="BD14" s="3">
-        <v>45814.89930555555</v>
+        <v>110</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>45814.875</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45814</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -3113,141 +2372,203 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="L15">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M15">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="N15">
-        <v>5.36</v>
+        <v>5.78</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T15">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V15">
+        <v>10</v>
+      </c>
+      <c r="W15">
+        <v>1.01</v>
+      </c>
+      <c r="X15">
+        <v>1.09</v>
+      </c>
+      <c r="Y15">
+        <v>7.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.44</v>
+      </c>
+      <c r="AA15">
+        <v>2.6</v>
+      </c>
+      <c r="AB15">
+        <v>2.4</v>
+      </c>
+      <c r="AC15">
+        <v>1.5</v>
+      </c>
+      <c r="AD15">
+        <v>4.6</v>
+      </c>
+      <c r="AE15">
+        <v>1.18</v>
+      </c>
+      <c r="AF15">
+        <v>2.33</v>
+      </c>
+      <c r="AG15">
+        <v>1.52</v>
+      </c>
+      <c r="AH15">
+        <v>9.75</v>
+      </c>
+      <c r="AI15">
+        <v>1.09</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>45814.89930555555</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="2">
+        <v>45814</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16">
+        <v>1.57</v>
+      </c>
+      <c r="M16">
+        <v>3.55</v>
+      </c>
+      <c r="N16">
+        <v>4.83</v>
+      </c>
+      <c r="O16">
+        <v>1.44</v>
+      </c>
+      <c r="P16">
+        <v>8.25</v>
+      </c>
+      <c r="Q16">
+        <v>3.25</v>
+      </c>
+      <c r="R16">
+        <v>1.39</v>
+      </c>
+      <c r="S16">
+        <v>2.7</v>
+      </c>
+      <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
+        <v>1.3</v>
+      </c>
+      <c r="V16">
+        <v>7.3</v>
+      </c>
+      <c r="W16">
+        <v>1.07</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>8.5</v>
+      </c>
+      <c r="Z16">
+        <v>1.35</v>
+      </c>
+      <c r="AA16">
+        <v>3</v>
+      </c>
+      <c r="AB16">
+        <v>2.05</v>
+      </c>
+      <c r="AC16">
+        <v>1.67</v>
+      </c>
+      <c r="AD16">
+        <v>3.8</v>
+      </c>
+      <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
+        <v>1.98</v>
+      </c>
+      <c r="AG16">
+        <v>1.7</v>
+      </c>
+      <c r="AH16">
         <v>6.5</v>
       </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.03</v>
-      </c>
-      <c r="Y15">
-        <v>9.25</v>
-      </c>
-      <c r="Z15">
-        <v>1.24</v>
-      </c>
-      <c r="AA15">
-        <v>3.34</v>
-      </c>
-      <c r="AB15">
-        <v>1.95</v>
-      </c>
-      <c r="AC15">
-        <v>1.75</v>
-      </c>
-      <c r="AD15">
-        <v>3.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.29</v>
-      </c>
-      <c r="AF15">
-        <v>1.88</v>
-      </c>
-      <c r="AG15">
-        <v>1.73</v>
-      </c>
-      <c r="AH15">
-        <v>6</v>
-      </c>
-      <c r="AI15">
-        <v>1.08</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>106</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL15">
-        <v>1.18</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>2.22</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-      <c r="BD15" s="3">
+      <c r="AI16">
+        <v>1.1</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45814.95833333334</v>
       </c>
     </row>
